--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T20:10:55+00:00</t>
+    <t>2026-06-24T07:44:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:44:07+00:00</t>
+    <t>2026-06-24T08:41:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:41:34+00:00</t>
+    <t>2026-06-24T09:41:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:41:40+00:00</t>
+    <t>2026-06-24T10:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:22:04+00:00</t>
+    <t>2026-06-24T10:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:24:31+00:00</t>
+    <t>2026-06-24T10:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:28:18+00:00</t>
+    <t>2026-06-24T10:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:33:28+00:00</t>
+    <t>2026-06-24T10:35:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/main/all-profiles.xlsx
+++ b/branches/main/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:35:58+00:00</t>
+    <t>2026-06-24T11:03:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
